--- a/산출물/99_제출파일/테이블_정의서.xlsx
+++ b/산출물/99_제출파일/테이블_정의서.xlsx
@@ -536,17 +536,17 @@
   <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1206,17 +1206,17 @@
   <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1621,7 +1621,7 @@
       <c r="H18" s="11" t="inlineStr"/>
       <c r="I18" s="12" t="inlineStr">
         <is>
-          <t>6자리 공유 코드(혼동문자 0/1/I/O 제외, crypto RNG)</t>
+          <t>6자리 공유 코드(혼동문자 제외)</t>
         </is>
       </c>
       <c r="J18" s="11" t="inlineStr"/>
@@ -1800,7 +1800,7 @@
       <c r="H23" s="11" t="inlineStr"/>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>공개곡 작성자(기본 "익명")</t>
+          <t>공개곡 작성자(기본 익명)</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr"/>
@@ -1835,7 +1835,7 @@
       <c r="H24" s="11" t="inlineStr"/>
       <c r="I24" s="12" t="inlineStr">
         <is>
-          <t>소유 검증·중복방지(외부 미노출)</t>
+          <t>소유 검증·중복방지</t>
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr"/>
@@ -1870,7 +1870,7 @@
       <c r="H25" s="11" t="inlineStr"/>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>파생곡 출처 크레딧. NULL이면 원곡</t>
+          <t>파생곡 출처. NULL=원곡</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
-          <t>자기참조(앱 레벨)</t>
+          <t>자기참조(앱)</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1987,7 @@
       <c r="H28" s="11" t="inlineStr"/>
       <c r="I28" s="12" t="inlineStr">
         <is>
-          <t>원곡 publish 중복방지(첫 트랙 해시)</t>
+          <t>원곡 중복방지 해시(첫 트랙)</t>
         </is>
       </c>
       <c r="J28" s="11" t="inlineStr"/>
@@ -2022,7 +2022,7 @@
       <c r="H29" s="11" t="inlineStr"/>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>중복방지 키 보강(트랙 수 다르면 다른 곡)</t>
+          <t>중복방지 보강(트랙 수)</t>
         </is>
       </c>
       <c r="J29" s="11" t="inlineStr"/>
@@ -2205,17 +2205,17 @@
   <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
-          <t>앱 레벨(FK 제약 없음)</t>
+          <t>앱 레벨</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       <c r="H21" s="11" t="inlineStr"/>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>노트 이벤트 JSON 배열(NoteEvent, 개요 시트)</t>
+          <t>노트 이벤트 JSON(개요 참조)</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr"/>
@@ -2776,7 +2776,7 @@
       <c r="H22" s="11" t="inlineStr"/>
       <c r="I22" s="12" t="inlineStr">
         <is>
-          <t>piano/guitar/bass/drum. 옛 행 NULL→클라 추론</t>
+          <t>piano/guitar/bass/drum</t>
         </is>
       </c>
       <c r="J22" s="11" t="inlineStr"/>
@@ -2811,7 +2811,7 @@
       <c r="H23" s="11" t="inlineStr"/>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>음색 프리셋(소리만, 음정 무관). 옛 행 NULL</t>
+          <t>음색 프리셋(소리만)</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr"/>
@@ -2846,7 +2846,7 @@
       <c r="H24" s="11" t="inlineStr"/>
       <c r="I24" s="12" t="inlineStr">
         <is>
-          <t>공개 세션 트랙 추가 시 소유 검증. 옛 행 NULL</t>
+          <t>트랙 소유 검증</t>
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr"/>
@@ -3000,17 +3000,17 @@
   <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="K19" s="11" t="inlineStr">
         <is>
-          <t>앱 레벨(FK 제약 없음)</t>
+          <t>앱 레벨</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       <c r="H20" s="11" t="inlineStr"/>
       <c r="I20" s="12" t="inlineStr">
         <is>
-          <t>동일인 같은 내용 60초 내 중복 작성 방지</t>
+          <t>60초 중복작성 방지</t>
         </is>
       </c>
       <c r="J20" s="11" t="inlineStr"/>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>1=숨김(서로 다른 신고자 임계 초과 시 자동)</t>
+          <t>1=숨김(신고 임계 자동)</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr"/>
@@ -3795,17 +3795,17 @@
   <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -4407,17 +4407,17 @@
   <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">

--- a/산출물/99_제출파일/테이블_정의서.xlsx
+++ b/산출물/99_제출파일/테이블_정의서.xlsx
@@ -576,7 +576,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>하모니 미니앱 DB · SQLite(node:sqlite, 외부 의존 없음) · 작성 김민혁(Backend) · 근거 apps/api/server.mjs · 2026-06-27</t>
+          <t>하모니 미니앱 DB · SQLite(node:sqlite, 외부 의존 없음) · 작성 김민혁(Backend) · 근거 apps/api/server.mjs · 2026-06-22</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       <c r="B7" s="4" t="n"/>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D7" s="7" t="n"/>
@@ -1262,7 +1262,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>하모니 미니앱 DB · SQLite(node:sqlite, 외부 의존 없음) · 작성 김민혁(Backend) · 근거 apps/api/server.mjs · 2026-06-27</t>
+          <t>하모니 미니앱 DB · SQLite(node:sqlite, 외부 의존 없음) · 작성 김민혁(Backend) · 근거 apps/api/server.mjs · 2026-06-22</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       <c r="B7" s="4" t="n"/>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D7" s="7" t="n"/>
@@ -2277,7 +2277,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>하모니 미니앱 DB · SQLite(node:sqlite, 외부 의존 없음) · 작성 김민혁(Backend) · 근거 apps/api/server.mjs · 2026-06-27</t>
+          <t>하모니 미니앱 DB · SQLite(node:sqlite, 외부 의존 없음) · 작성 김민혁(Backend) · 근거 apps/api/server.mjs · 2026-06-22</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
       <c r="B7" s="4" t="n"/>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D7" s="7" t="n"/>
@@ -3088,7 +3088,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>하모니 미니앱 DB · SQLite(node:sqlite, 외부 의존 없음) · 작성 김민혁(Backend) · 근거 apps/api/server.mjs · 2026-06-27</t>
+          <t>하모니 미니앱 DB · SQLite(node:sqlite, 외부 의존 없음) · 작성 김민혁(Backend) · 근거 apps/api/server.mjs · 2026-06-22</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       <c r="B7" s="4" t="n"/>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D7" s="7" t="n"/>
@@ -3899,7 +3899,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>하모니 미니앱 DB · SQLite(node:sqlite, 외부 의존 없음) · 작성 김민혁(Backend) · 근거 apps/api/server.mjs · 2026-06-27</t>
+          <t>하모니 미니앱 DB · SQLite(node:sqlite, 외부 의존 없음) · 작성 김민혁(Backend) · 근거 apps/api/server.mjs · 2026-06-22</t>
         </is>
       </c>
     </row>
@@ -3971,7 +3971,7 @@
       <c r="B7" s="4" t="n"/>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D7" s="7" t="n"/>
@@ -4527,7 +4527,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>하모니 미니앱 DB · SQLite(node:sqlite, 외부 의존 없음) · 작성 김민혁(Backend) · 근거 apps/api/server.mjs · 2026-06-27</t>
+          <t>하모니 미니앱 DB · SQLite(node:sqlite, 외부 의존 없음) · 작성 김민혁(Backend) · 근거 apps/api/server.mjs · 2026-06-22</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4599,7 @@
       <c r="B7" s="4" t="n"/>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D7" s="7" t="n"/>

--- a/산출물/99_제출파일/테이블_정의서.xlsx
+++ b/산출물/99_제출파일/테이블_정의서.xlsx
@@ -102,7 +102,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE7F0FF"/>
+        <fgColor rgb="FFE8F3FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -121,16 +121,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFD7DCE2"/>
+        <color rgb="FFE5E8EB"/>
       </left>
       <right style="thin">
-        <color rgb="FFD7DCE2"/>
+        <color rgb="FFE5E8EB"/>
       </right>
       <top style="thin">
-        <color rgb="FFD7DCE2"/>
+        <color rgb="FFE5E8EB"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFD7DCE2"/>
+        <color rgb="FFE5E8EB"/>
       </bottom>
     </border>
   </borders>
@@ -956,7 +956,7 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>events 컬럼 — NoteEvent JSON 계약 (저장 형식: {tick, phase, chord, source})</t>
+          <t>events 컬럼 · NoteEvent JSON 계약 (저장 형식: {tick, phase, chord, source})</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
